--- a/settlements/obex/2026-07/obex_settlement_july_2026.xlsx
+++ b/settlements/obex/2026-07/obex_settlement_july_2026.xlsx
@@ -979,7 +979,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
